--- a/res/vuz/sut.xlsx
+++ b/res/vuz/sut.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC50E443-97EE-4696-BBF1-098252F05195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0410ACA-EDA3-480B-A78E-A138CD35BA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="305">
   <si>
     <t>#name</t>
   </si>
@@ -1718,9 +1718,6 @@
       <c r="E25" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1738,9 +1735,6 @@
       <c r="E26" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1758,9 +1752,6 @@
       <c r="E27" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -1778,9 +1769,6 @@
       <c r="E28" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1798,9 +1786,6 @@
       <c r="E29" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1818,9 +1803,6 @@
       <c r="E30" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1838,9 +1820,6 @@
       <c r="E31" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -1858,11 +1837,8 @@
       <c r="E32" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>252</v>
       </c>
@@ -1878,11 +1854,8 @@
       <c r="E33" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>252</v>
       </c>
@@ -1898,11 +1871,8 @@
       <c r="E34" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>252</v>
       </c>
@@ -1918,11 +1888,8 @@
       <c r="E35" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>252</v>
       </c>
@@ -1938,11 +1905,8 @@
       <c r="E36" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>252</v>
       </c>
@@ -1958,11 +1922,8 @@
       <c r="E37" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>252</v>
       </c>
@@ -1978,11 +1939,8 @@
       <c r="E38" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>252</v>
       </c>
@@ -1998,11 +1956,8 @@
       <c r="E39" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>252</v>
       </c>
@@ -2018,11 +1973,8 @@
       <c r="E40" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>252</v>
       </c>
@@ -2038,11 +1990,8 @@
       <c r="E41" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>252</v>
       </c>
@@ -2058,11 +2007,8 @@
       <c r="E42" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>252</v>
       </c>
@@ -2078,11 +2024,8 @@
       <c r="E43" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>252</v>
       </c>
@@ -2098,11 +2041,8 @@
       <c r="E44" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>252</v>
       </c>
@@ -2118,11 +2058,8 @@
       <c r="E45" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>252</v>
       </c>
@@ -2138,11 +2075,8 @@
       <c r="E46" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>252</v>
       </c>
@@ -2158,11 +2092,8 @@
       <c r="E47" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>252</v>
       </c>
@@ -2178,11 +2109,8 @@
       <c r="E48" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>252</v>
       </c>
@@ -2198,11 +2126,8 @@
       <c r="E49" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>252</v>
       </c>
@@ -2218,11 +2143,8 @@
       <c r="E50" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>252</v>
       </c>
@@ -2238,11 +2160,8 @@
       <c r="E51" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>252</v>
       </c>
@@ -2258,11 +2177,8 @@
       <c r="E52" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>252</v>
       </c>
@@ -2278,11 +2194,8 @@
       <c r="E53" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>252</v>
       </c>
@@ -2298,11 +2211,8 @@
       <c r="E54" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>252</v>
       </c>
@@ -2318,11 +2228,8 @@
       <c r="E55" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>252</v>
       </c>
@@ -2338,11 +2245,8 @@
       <c r="E56" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>252</v>
       </c>
@@ -2358,11 +2262,8 @@
       <c r="E57" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>252</v>
       </c>
@@ -2378,11 +2279,8 @@
       <c r="E58" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>252</v>
       </c>
@@ -2398,11 +2296,8 @@
       <c r="E59" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>252</v>
       </c>
@@ -2418,11 +2313,8 @@
       <c r="E60" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>158</v>
       </c>
@@ -2438,11 +2330,8 @@
       <c r="E61" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>158</v>
       </c>
@@ -2458,11 +2347,8 @@
       <c r="E62" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>158</v>
       </c>
@@ -2478,11 +2364,8 @@
       <c r="E63" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>158</v>
       </c>
@@ -2498,11 +2381,8 @@
       <c r="E64" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>252</v>
       </c>
@@ -2518,11 +2398,8 @@
       <c r="E65" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>252</v>
       </c>
@@ -2538,11 +2415,8 @@
       <c r="E66" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>158</v>
       </c>
@@ -2558,11 +2432,8 @@
       <c r="E67" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>252</v>
       </c>
@@ -2578,11 +2449,8 @@
       <c r="E68" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>252</v>
       </c>
@@ -2598,11 +2466,8 @@
       <c r="E69" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>252</v>
       </c>
@@ -2618,11 +2483,8 @@
       <c r="E70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>252</v>
       </c>
@@ -2638,11 +2500,8 @@
       <c r="E71" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>158</v>
       </c>
@@ -2658,11 +2517,8 @@
       <c r="E72" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>158</v>
       </c>
@@ -2678,11 +2534,8 @@
       <c r="E73" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>252</v>
       </c>
@@ -2698,11 +2551,8 @@
       <c r="E74" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>252</v>
       </c>
@@ -2718,11 +2568,8 @@
       <c r="E75" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>252</v>
       </c>
@@ -2738,11 +2585,8 @@
       <c r="E76" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>252</v>
       </c>
@@ -2758,11 +2602,8 @@
       <c r="E77" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>252</v>
       </c>
@@ -2778,11 +2619,8 @@
       <c r="E78" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>252</v>
       </c>
@@ -2798,11 +2636,8 @@
       <c r="E79" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>252</v>
       </c>
@@ -2818,11 +2653,8 @@
       <c r="E80" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>252</v>
       </c>
@@ -2838,11 +2670,8 @@
       <c r="E81" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>252</v>
       </c>
@@ -2858,11 +2687,8 @@
       <c r="E82" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>252</v>
       </c>
@@ -2878,11 +2704,8 @@
       <c r="E83" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>252</v>
       </c>
@@ -2898,11 +2721,8 @@
       <c r="E84" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>158</v>
       </c>
@@ -2918,11 +2738,8 @@
       <c r="E85" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>252</v>
       </c>
@@ -2938,11 +2755,8 @@
       <c r="E86" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>252</v>
       </c>
@@ -2958,11 +2772,8 @@
       <c r="E87" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>252</v>
       </c>
@@ -2978,11 +2789,8 @@
       <c r="E88" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>252</v>
       </c>
@@ -2998,11 +2806,8 @@
       <c r="E89" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>158</v>
       </c>
@@ -3018,11 +2823,8 @@
       <c r="E90" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>158</v>
       </c>
@@ -3038,11 +2840,8 @@
       <c r="E91" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>252</v>
       </c>
@@ -3058,11 +2857,8 @@
       <c r="E92" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>158</v>
       </c>
@@ -3078,11 +2874,8 @@
       <c r="E93" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>252</v>
       </c>
@@ -3098,11 +2891,8 @@
       <c r="E94" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>252</v>
       </c>
@@ -3118,11 +2908,8 @@
       <c r="E95" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>252</v>
       </c>
@@ -3138,11 +2925,8 @@
       <c r="E96" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>252</v>
       </c>
@@ -3158,11 +2942,8 @@
       <c r="E97" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>252</v>
       </c>
@@ -3178,11 +2959,8 @@
       <c r="E98" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>158</v>
       </c>
@@ -3198,11 +2976,8 @@
       <c r="E99" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>158</v>
       </c>
@@ -3218,11 +2993,8 @@
       <c r="E100" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>158</v>
       </c>
@@ -3238,11 +3010,8 @@
       <c r="E101" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>158</v>
       </c>
@@ -3258,11 +3027,8 @@
       <c r="E102" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>158</v>
       </c>
@@ -3278,11 +3044,8 @@
       <c r="E103" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>158</v>
       </c>
@@ -3298,11 +3061,8 @@
       <c r="E104" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>252</v>
       </c>
@@ -3318,11 +3078,8 @@
       <c r="E105" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>158</v>
       </c>
@@ -3338,11 +3095,8 @@
       <c r="E106" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>252</v>
       </c>
@@ -3358,11 +3112,8 @@
       <c r="E107" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F107" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>252</v>
       </c>
@@ -3378,11 +3129,8 @@
       <c r="E108" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>252</v>
       </c>
@@ -3398,11 +3146,8 @@
       <c r="E109" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>252</v>
       </c>
@@ -3418,11 +3163,8 @@
       <c r="E110" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>252</v>
       </c>
@@ -3438,11 +3180,8 @@
       <c r="E111" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F111" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>252</v>
       </c>
@@ -3458,11 +3197,8 @@
       <c r="E112" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>252</v>
       </c>
@@ -3478,11 +3214,8 @@
       <c r="E113" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>252</v>
       </c>
@@ -3498,11 +3231,8 @@
       <c r="E114" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>252</v>
       </c>
@@ -3518,11 +3248,8 @@
       <c r="E115" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>252</v>
       </c>
@@ -3538,11 +3265,8 @@
       <c r="E116" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>252</v>
       </c>
@@ -3558,11 +3282,8 @@
       <c r="E117" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>252</v>
       </c>
@@ -3578,11 +3299,8 @@
       <c r="E118" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F118" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>252</v>
       </c>
@@ -3598,11 +3316,8 @@
       <c r="E119" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>252</v>
       </c>
@@ -3618,11 +3333,8 @@
       <c r="E120" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F120" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>252</v>
       </c>
@@ -3638,11 +3350,8 @@
       <c r="E121" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>252</v>
       </c>
@@ -3658,11 +3367,8 @@
       <c r="E122" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>252</v>
       </c>
@@ -3678,11 +3384,8 @@
       <c r="E123" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F123" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>252</v>
       </c>
@@ -3698,11 +3401,8 @@
       <c r="E124" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>252</v>
       </c>
@@ -3718,11 +3418,8 @@
       <c r="E125" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F125" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>252</v>
       </c>
@@ -3738,11 +3435,8 @@
       <c r="E126" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
@@ -3758,11 +3452,8 @@
       <c r="E127" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>252</v>
       </c>
@@ -3778,11 +3469,8 @@
       <c r="E128" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>252</v>
       </c>
@@ -3798,11 +3486,8 @@
       <c r="E129" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F129" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>252</v>
       </c>
@@ -3818,11 +3503,8 @@
       <c r="E130" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>158</v>
       </c>
@@ -3838,11 +3520,8 @@
       <c r="E131" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>252</v>
       </c>
@@ -3858,11 +3537,8 @@
       <c r="E132" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>252</v>
       </c>
@@ -3878,11 +3554,8 @@
       <c r="E133" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>158</v>
       </c>
@@ -3898,11 +3571,8 @@
       <c r="E134" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>158</v>
       </c>
@@ -3918,11 +3588,8 @@
       <c r="E135" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>252</v>
       </c>
@@ -3938,11 +3605,8 @@
       <c r="E136" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>252</v>
       </c>
@@ -3958,11 +3622,8 @@
       <c r="E137" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>252</v>
       </c>
@@ -3978,11 +3639,8 @@
       <c r="E138" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>158</v>
       </c>
@@ -3998,11 +3656,8 @@
       <c r="E139" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F139" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>158</v>
       </c>
@@ -4018,11 +3673,8 @@
       <c r="E140" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>252</v>
       </c>
@@ -4038,11 +3690,8 @@
       <c r="E141" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>158</v>
       </c>
@@ -4058,11 +3707,8 @@
       <c r="E142" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>158</v>
       </c>
@@ -4078,11 +3724,8 @@
       <c r="E143" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F143" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>252</v>
       </c>
@@ -4098,11 +3741,8 @@
       <c r="E144" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>252</v>
       </c>
@@ -4118,11 +3758,8 @@
       <c r="E145" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F145" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>252</v>
       </c>
@@ -4138,11 +3775,8 @@
       <c r="E146" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F146" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>158</v>
       </c>
@@ -4158,11 +3792,8 @@
       <c r="E147" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F147" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>252</v>
       </c>
@@ -4178,11 +3809,8 @@
       <c r="E148" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F148" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>252</v>
       </c>
@@ -4198,11 +3826,8 @@
       <c r="E149" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F149" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>158</v>
       </c>
@@ -4218,11 +3843,8 @@
       <c r="E150" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F150" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>158</v>
       </c>
@@ -4238,11 +3860,8 @@
       <c r="E151" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>252</v>
       </c>
@@ -4258,11 +3877,8 @@
       <c r="E152" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F152" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>252</v>
       </c>
@@ -4278,11 +3894,8 @@
       <c r="E153" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F153" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>252</v>
       </c>
@@ -4298,11 +3911,8 @@
       <c r="E154" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F154" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>252</v>
       </c>
@@ -4318,11 +3928,8 @@
       <c r="E155" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F155" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>252</v>
       </c>
@@ -4338,11 +3945,8 @@
       <c r="E156" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F156" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>252</v>
       </c>
@@ -4358,11 +3962,8 @@
       <c r="E157" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F157" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>158</v>
       </c>
@@ -4378,11 +3979,8 @@
       <c r="E158" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>158</v>
       </c>
@@ -4398,11 +3996,8 @@
       <c r="E159" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F159" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>252</v>
       </c>
@@ -4418,11 +4013,8 @@
       <c r="E160" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F160" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>252</v>
       </c>
@@ -4438,11 +4030,8 @@
       <c r="E161" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F161" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>252</v>
       </c>
@@ -4458,11 +4047,8 @@
       <c r="E162" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F162" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>252</v>
       </c>
@@ -4478,11 +4064,8 @@
       <c r="E163" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F163" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>252</v>
       </c>
@@ -4498,11 +4081,8 @@
       <c r="E164" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F164" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>252</v>
       </c>
@@ -4518,11 +4098,8 @@
       <c r="E165" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F165" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>158</v>
       </c>
@@ -4538,11 +4115,8 @@
       <c r="E166" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F166" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>158</v>
       </c>
@@ -4558,11 +4132,8 @@
       <c r="E167" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F167" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>252</v>
       </c>
@@ -4578,11 +4149,8 @@
       <c r="E168" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F168" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>252</v>
       </c>
@@ -4598,11 +4166,8 @@
       <c r="E169" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F169" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>158</v>
       </c>
@@ -4618,11 +4183,8 @@
       <c r="E170" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F170" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>252</v>
       </c>
@@ -4638,11 +4200,8 @@
       <c r="E171" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F171" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>252</v>
       </c>
@@ -4658,11 +4217,8 @@
       <c r="E172" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F172" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>252</v>
       </c>
@@ -4678,11 +4234,8 @@
       <c r="E173" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F173" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>252</v>
       </c>
@@ -4698,11 +4251,8 @@
       <c r="E174" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F174" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>158</v>
       </c>
@@ -4718,11 +4268,8 @@
       <c r="E175" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>252</v>
       </c>
@@ -4738,11 +4285,8 @@
       <c r="E176" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>252</v>
       </c>
@@ -4758,11 +4302,8 @@
       <c r="E177" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F177" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>252</v>
       </c>
@@ -4778,11 +4319,8 @@
       <c r="E178" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F178" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>252</v>
       </c>
@@ -4798,11 +4336,8 @@
       <c r="E179" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F179" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>158</v>
       </c>
@@ -4818,11 +4353,8 @@
       <c r="E180" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>158</v>
       </c>
@@ -4838,11 +4370,8 @@
       <c r="E181" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F181" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>158</v>
       </c>
@@ -4858,11 +4387,8 @@
       <c r="E182" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F182" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>158</v>
       </c>
@@ -4878,11 +4404,8 @@
       <c r="E183" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F183" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>158</v>
       </c>
@@ -4898,11 +4421,8 @@
       <c r="E184" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F184" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>158</v>
       </c>
@@ -4918,11 +4438,8 @@
       <c r="E185" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F185" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>158</v>
       </c>
@@ -4938,11 +4455,8 @@
       <c r="E186" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F186" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>158</v>
       </c>
@@ -4958,11 +4472,8 @@
       <c r="E187" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F187" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>158</v>
       </c>
@@ -4978,11 +4489,8 @@
       <c r="E188" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F188" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>252</v>
       </c>
@@ -4998,11 +4506,8 @@
       <c r="E189" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F189" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>252</v>
       </c>
@@ -5018,11 +4523,8 @@
       <c r="E190" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F190" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>252</v>
       </c>
@@ -5038,11 +4540,8 @@
       <c r="E191" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F191" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>252</v>
       </c>
@@ -5058,11 +4557,8 @@
       <c r="E192" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F192" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>158</v>
       </c>
@@ -5078,11 +4574,8 @@
       <c r="E193" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F193" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>158</v>
       </c>
@@ -5098,11 +4591,8 @@
       <c r="E194" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F194" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>252</v>
       </c>
@@ -5118,11 +4608,8 @@
       <c r="E195" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F195" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>252</v>
       </c>
@@ -5138,11 +4625,8 @@
       <c r="E196" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F196" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>158</v>
       </c>
@@ -5158,11 +4642,8 @@
       <c r="E197" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F197" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>158</v>
       </c>
@@ -5178,11 +4659,8 @@
       <c r="E198" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F198" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>252</v>
       </c>
@@ -5198,11 +4676,8 @@
       <c r="E199" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F199" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>252</v>
       </c>
@@ -5218,11 +4693,8 @@
       <c r="E200" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F200" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>158</v>
       </c>
@@ -5238,11 +4710,8 @@
       <c r="E201" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F201" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>252</v>
       </c>
@@ -5258,11 +4727,8 @@
       <c r="E202" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F202" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>252</v>
       </c>
@@ -5278,11 +4744,8 @@
       <c r="E203" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F203" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>252</v>
       </c>
@@ -5298,11 +4761,8 @@
       <c r="E204" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F204" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>158</v>
       </c>
@@ -5318,11 +4778,8 @@
       <c r="E205" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F205" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>252</v>
       </c>
@@ -5338,11 +4795,8 @@
       <c r="E206" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F206" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>252</v>
       </c>
@@ -5358,11 +4812,8 @@
       <c r="E207" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="F207" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>252</v>
       </c>
@@ -5378,11 +4829,8 @@
       <c r="E208" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F208" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>252</v>
       </c>
@@ -5398,11 +4846,8 @@
       <c r="E209" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F209" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>252</v>
       </c>
@@ -5418,11 +4863,8 @@
       <c r="E210" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F210" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>252</v>
       </c>
@@ -5438,11 +4880,8 @@
       <c r="E211" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F211" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>158</v>
       </c>
@@ -5458,11 +4897,8 @@
       <c r="E212" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F212" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>158</v>
       </c>
@@ -5478,11 +4914,8 @@
       <c r="E213" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F213" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>252</v>
       </c>
@@ -5498,11 +4931,8 @@
       <c r="E214" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F214" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>252</v>
       </c>
@@ -5518,11 +4948,8 @@
       <c r="E215" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F215" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>252</v>
       </c>
@@ -5538,11 +4965,8 @@
       <c r="E216" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F216" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>252</v>
       </c>
@@ -5558,11 +4982,8 @@
       <c r="E217" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F217" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>252</v>
       </c>
@@ -5578,11 +4999,8 @@
       <c r="E218" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F218" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>252</v>
       </c>
@@ -5598,11 +5016,8 @@
       <c r="E219" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F219" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>252</v>
       </c>
@@ -5618,11 +5033,8 @@
       <c r="E220" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F220" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>158</v>
       </c>
@@ -5638,11 +5050,8 @@
       <c r="E221" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F221" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>158</v>
       </c>
@@ -5658,11 +5067,8 @@
       <c r="E222" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F222" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>158</v>
       </c>
@@ -5678,11 +5084,8 @@
       <c r="E223" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F223" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>252</v>
       </c>
@@ -5698,11 +5101,8 @@
       <c r="E224" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F224" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>158</v>
       </c>
@@ -5718,11 +5118,8 @@
       <c r="E225" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F225" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>158</v>
       </c>
@@ -5738,11 +5135,8 @@
       <c r="E226" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F226" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>158</v>
       </c>
@@ -5758,11 +5152,8 @@
       <c r="E227" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F227" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>158</v>
       </c>
@@ -5778,11 +5169,8 @@
       <c r="E228" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F228" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>158</v>
       </c>
@@ -5798,11 +5186,8 @@
       <c r="E229" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F229" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>158</v>
       </c>
@@ -5818,11 +5203,8 @@
       <c r="E230" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F230" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>252</v>
       </c>
@@ -5838,11 +5220,8 @@
       <c r="E231" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F231" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>252</v>
       </c>
@@ -5858,11 +5237,8 @@
       <c r="E232" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F232" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>252</v>
       </c>
@@ -5878,11 +5254,8 @@
       <c r="E233" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F233" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>252</v>
       </c>
@@ -5898,11 +5271,8 @@
       <c r="E234" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F234" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>158</v>
       </c>
@@ -5918,11 +5288,8 @@
       <c r="E235" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F235" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>252</v>
       </c>
@@ -5938,11 +5305,8 @@
       <c r="E236" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F236" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>158</v>
       </c>
@@ -5958,11 +5322,8 @@
       <c r="E237" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F237" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>158</v>
       </c>
@@ -5978,11 +5339,8 @@
       <c r="E238" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F238" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>252</v>
       </c>
@@ -5998,11 +5356,8 @@
       <c r="E239" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F239" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>252</v>
       </c>
@@ -6018,11 +5373,8 @@
       <c r="E240" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F240" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>252</v>
       </c>
@@ -6038,11 +5390,8 @@
       <c r="E241" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F241" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>158</v>
       </c>
@@ -6058,11 +5407,8 @@
       <c r="E242" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F242" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>158</v>
       </c>
@@ -6078,11 +5424,8 @@
       <c r="E243" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F243" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>252</v>
       </c>
@@ -6098,11 +5441,8 @@
       <c r="E244" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F244" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>252</v>
       </c>
@@ -6118,11 +5458,8 @@
       <c r="E245" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F245" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>158</v>
       </c>
@@ -6138,11 +5475,8 @@
       <c r="E246" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F246" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>252</v>
       </c>
@@ -6158,11 +5492,8 @@
       <c r="E247" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F247" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>252</v>
       </c>
@@ -6178,11 +5509,8 @@
       <c r="E248" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F248" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>252</v>
       </c>
@@ -6198,11 +5526,8 @@
       <c r="E249" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F249" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>252</v>
       </c>
@@ -6218,11 +5543,8 @@
       <c r="E250" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F250" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>252</v>
       </c>
@@ -6238,11 +5560,8 @@
       <c r="E251" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F251" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>252</v>
       </c>
@@ -6258,11 +5577,8 @@
       <c r="E252" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F252" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>252</v>
       </c>
@@ -6278,11 +5594,8 @@
       <c r="E253" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F253" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>252</v>
       </c>
@@ -6298,11 +5611,8 @@
       <c r="E254" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F254" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>252</v>
       </c>
@@ -6318,11 +5628,8 @@
       <c r="E255" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F255" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>252</v>
       </c>
@@ -6338,11 +5645,8 @@
       <c r="E256" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F256" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>158</v>
       </c>
@@ -6358,11 +5662,8 @@
       <c r="E257" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F257" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>252</v>
       </c>
@@ -6378,11 +5679,8 @@
       <c r="E258" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F258" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>252</v>
       </c>
@@ -6398,11 +5696,8 @@
       <c r="E259" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F259" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>252</v>
       </c>
@@ -6418,11 +5713,8 @@
       <c r="E260" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F260" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>252</v>
       </c>
@@ -6438,11 +5730,8 @@
       <c r="E261" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F261" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>252</v>
       </c>
@@ -6458,11 +5747,8 @@
       <c r="E262" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F262" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>252</v>
       </c>
@@ -6478,11 +5764,8 @@
       <c r="E263" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F263" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>252</v>
       </c>
@@ -6498,11 +5781,8 @@
       <c r="E264" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F264" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>252</v>
       </c>
@@ -6518,11 +5798,8 @@
       <c r="E265" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F265" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>158</v>
       </c>
@@ -6538,11 +5815,8 @@
       <c r="E266" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F266" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>158</v>
       </c>
@@ -6558,11 +5832,8 @@
       <c r="E267" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F267" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>252</v>
       </c>
@@ -6578,11 +5849,8 @@
       <c r="E268" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F268" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>158</v>
       </c>
@@ -6598,11 +5866,8 @@
       <c r="E269" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F269" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>158</v>
       </c>
@@ -6618,11 +5883,8 @@
       <c r="E270" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F270" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>252</v>
       </c>
@@ -6638,11 +5900,8 @@
       <c r="E271" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F271" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>252</v>
       </c>
@@ -6658,9 +5917,6 @@
       <c r="E272" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F272" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
@@ -6678,9 +5934,6 @@
       <c r="E273" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F273" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
@@ -6698,9 +5951,6 @@
       <c r="E274" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F274" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
@@ -6718,9 +5968,6 @@
       <c r="E275" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F275" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
@@ -6738,9 +5985,6 @@
       <c r="E276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F276" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
@@ -6758,9 +6002,6 @@
       <c r="E277" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F277" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
@@ -6778,9 +6019,6 @@
       <c r="E278" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F278" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
@@ -6798,9 +6036,6 @@
       <c r="E279" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F279" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
@@ -6817,9 +6052,6 @@
       </c>
       <c r="E280" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
